--- a/master_volunteers.xlsx
+++ b/master_volunteers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gyt_system\zhiban_cloud_system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67433DBA-3F2B-4344-9B2F-DDCD90CE9DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B393AF2F-18B3-4172-A7E7-4A5A62786BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="volunteers" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">volunteers!$A$1:$O$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">volunteers!$A$1:$O$211</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="857">
   <si>
     <t>分会</t>
   </si>
@@ -1186,9 +1186,6 @@
     <t>STW-160</t>
   </si>
   <si>
-    <t>张国齐</t>
-  </si>
-  <si>
     <t>0126342109</t>
   </si>
   <si>
@@ -2147,30 +2144,6 @@
   </si>
   <si>
     <t>740501-10-5569</t>
-  </si>
-  <si>
-    <t>CHE-160A</t>
-  </si>
-  <si>
-    <t>杨远铧</t>
-  </si>
-  <si>
-    <t>0166471627</t>
-  </si>
-  <si>
-    <t>Yong Yuen Wah</t>
-  </si>
-  <si>
-    <t>670826-10-5611</t>
-  </si>
-  <si>
-    <t>CHE-160B</t>
-  </si>
-  <si>
-    <t>冯珖玹</t>
-  </si>
-  <si>
-    <t>0122602988</t>
   </si>
   <si>
     <t>STW-161</t>
@@ -2618,6 +2591,14 @@
   </si>
   <si>
     <t>01135899100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄国齐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄国齐</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3010,7 +2991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O213"/>
+  <dimension ref="A1:O211"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4824,7 +4805,7 @@
         <v>224</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>21</v>
@@ -5209,7 +5190,7 @@
       </c>
       <c r="J51" s="3"/>
       <c r="K51" s="4" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>21</v>
@@ -6269,13 +6250,13 @@
         <v>386</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>387</v>
+        <v>855</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>20</v>
@@ -6287,11 +6268,11 @@
         <v>386</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>387</v>
+        <v>856</v>
       </c>
       <c r="J77" s="3"/>
       <c r="K77" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L77" s="3" t="s">
         <v>21</v>
@@ -6305,17 +6286,17 @@
         <v>114</v>
       </c>
       <c r="B78" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>391</v>
-      </c>
       <c r="F78" s="3" t="s">
         <v>20</v>
       </c>
@@ -6323,14 +6304,14 @@
         <v>20</v>
       </c>
       <c r="H78" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="I78" s="3" t="s">
         <v>389</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>390</v>
       </c>
       <c r="J78" s="3"/>
       <c r="K78" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L78" s="3" t="s">
         <v>21</v>
@@ -6344,41 +6325,41 @@
         <v>15</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E79" s="3" t="s">
+      <c r="F79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="J79" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="I79" s="3" t="s">
+      <c r="K79" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="K79" s="3" t="s">
-        <v>394</v>
       </c>
       <c r="L79" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O79" s="3"/>
     </row>
@@ -6387,41 +6368,41 @@
         <v>15</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="D80" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E80" s="3" t="s">
+      <c r="F80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J80" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="I80" s="3" t="s">
+      <c r="K80" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="K80" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="L80" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M80" s="3"/>
       <c r="N80" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O80" s="3"/>
     </row>
@@ -6430,41 +6411,41 @@
         <v>15</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="D81" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E81" s="3" t="s">
+      <c r="F81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="J81" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="I81" s="3" t="s">
+      <c r="K81" s="3" t="s">
         <v>403</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>404</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M81" s="3"/>
       <c r="N81" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="O81" s="3"/>
     </row>
@@ -6473,41 +6454,41 @@
         <v>15</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="D82" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E82" s="3" t="s">
+      <c r="F82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="I82" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="I82" s="3" t="s">
+      <c r="J82" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="J82" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="K82" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="L82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M82" s="3"/>
       <c r="N82" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="O82" s="3"/>
     </row>
@@ -6516,41 +6497,41 @@
         <v>15</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E83" s="3" t="s">
+      <c r="F83" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="J83" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="I83" s="3" t="s">
+      <c r="K83" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M83" s="3"/>
       <c r="N83" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="O83" s="3"/>
     </row>
@@ -6559,41 +6540,41 @@
         <v>15</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="D84" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E84" s="3" t="s">
+      <c r="F84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="J84" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="F84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="I84" s="3" t="s">
+      <c r="K84" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="K84" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="L84" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M84" s="3"/>
       <c r="N84" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="O84" s="3"/>
     </row>
@@ -6602,41 +6583,41 @@
         <v>15</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E85" s="3" t="s">
+      <c r="F85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="J85" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="F85" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="I85" s="3" t="s">
+      <c r="K85" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="J85" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="K85" s="3" t="s">
-        <v>425</v>
       </c>
       <c r="L85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M85" s="3"/>
       <c r="N85" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O85" s="3"/>
     </row>
@@ -6645,41 +6626,41 @@
         <v>15</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="D86" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="D86" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E86" s="3" t="s">
+      <c r="F86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="J86" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="F86" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="I86" s="3" t="s">
+      <c r="K86" s="3" t="s">
         <v>429</v>
-      </c>
-      <c r="J86" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="K86" s="3" t="s">
-        <v>430</v>
       </c>
       <c r="L86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M86" s="3"/>
       <c r="N86" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="O86" s="3"/>
     </row>
@@ -6688,41 +6669,41 @@
         <v>15</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="D87" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E87" s="3" t="s">
+      <c r="F87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="J87" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="F87" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="I87" s="3" t="s">
+      <c r="K87" s="3" t="s">
         <v>434</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="K87" s="3" t="s">
-        <v>435</v>
       </c>
       <c r="L87" s="3" t="s">
         <v>21</v>
       </c>
       <c r="M87" s="3"/>
       <c r="N87" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="O87" s="3"/>
     </row>
@@ -6731,37 +6712,37 @@
         <v>114</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>439</v>
       </c>
       <c r="D88" s="3"/>
       <c r="E88" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="K88" s="3" t="s">
         <v>439</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="K88" s="3" t="s">
-        <v>440</v>
       </c>
       <c r="L88" s="3"/>
       <c r="M88" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="N88" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="N88" s="3" t="s">
-        <v>444</v>
       </c>
       <c r="O88" s="3"/>
     </row>
@@ -6770,37 +6751,37 @@
         <v>15</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>445</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>446</v>
       </c>
       <c r="D89" s="3"/>
       <c r="E89" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="K89" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>447</v>
       </c>
       <c r="L89" s="3"/>
       <c r="M89" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N89" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O89" s="3"/>
     </row>
@@ -6809,37 +6790,37 @@
         <v>15</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>451</v>
       </c>
       <c r="D90" s="3"/>
       <c r="E90" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="K90" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="J90" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="K90" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="L90" s="3"/>
       <c r="M90" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N90" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O90" s="3"/>
     </row>
@@ -6848,37 +6829,37 @@
         <v>114</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="D91" s="3"/>
       <c r="E91" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H91" s="3"/>
       <c r="I91" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="K91" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>457</v>
       </c>
       <c r="L91" s="3"/>
       <c r="M91" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="O91" s="3"/>
     </row>
@@ -6887,37 +6868,37 @@
         <v>15</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>461</v>
       </c>
       <c r="D92" s="3"/>
       <c r="E92" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H92" s="3"/>
       <c r="I92" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="K92" s="3" t="s">
         <v>461</v>
-      </c>
-      <c r="J92" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="K92" s="3" t="s">
-        <v>462</v>
       </c>
       <c r="L92" s="3"/>
       <c r="M92" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N92" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="O92" s="3"/>
     </row>
@@ -6926,37 +6907,37 @@
         <v>114</v>
       </c>
       <c r="B93" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>465</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>466</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="K93" s="3" t="s">
         <v>466</v>
-      </c>
-      <c r="J93" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="K93" s="3" t="s">
-        <v>467</v>
       </c>
       <c r="L93" s="3"/>
       <c r="M93" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N93" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O93" s="3"/>
     </row>
@@ -6965,37 +6946,37 @@
         <v>114</v>
       </c>
       <c r="B94" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>470</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="K94" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>472</v>
       </c>
       <c r="L94" s="3"/>
       <c r="M94" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N94" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="O94" s="3"/>
     </row>
@@ -7004,37 +6985,37 @@
         <v>114</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>475</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>476</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="K95" s="3" t="s">
         <v>476</v>
-      </c>
-      <c r="J95" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="K95" s="3" t="s">
-        <v>477</v>
       </c>
       <c r="L95" s="3"/>
       <c r="M95" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N95" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="O95" s="3"/>
     </row>
@@ -7043,37 +7024,37 @@
         <v>15</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>480</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>481</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="K96" s="3" t="s">
         <v>481</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>482</v>
       </c>
       <c r="L96" s="3"/>
       <c r="M96" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="O96" s="3"/>
     </row>
@@ -7082,37 +7063,37 @@
         <v>15</v>
       </c>
       <c r="B97" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>486</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="K97" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="J97" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="K97" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="L97" s="3"/>
       <c r="M97" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O97" s="3"/>
     </row>
@@ -7121,37 +7102,37 @@
         <v>114</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>490</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>491</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="K98" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="J98" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="K98" s="3" t="s">
-        <v>492</v>
       </c>
       <c r="L98" s="3"/>
       <c r="M98" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="O98" s="3"/>
     </row>
@@ -7160,37 +7141,37 @@
         <v>15</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>496</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="K99" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="J99" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="K99" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="L99" s="3"/>
       <c r="M99" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N99" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="O99" s="3"/>
     </row>
@@ -7199,37 +7180,37 @@
         <v>15</v>
       </c>
       <c r="B100" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>500</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>501</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H100" s="3"/>
       <c r="I100" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="K100" s="3" t="s">
         <v>501</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>502</v>
       </c>
       <c r="L100" s="3"/>
       <c r="M100" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N100" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="O100" s="3"/>
     </row>
@@ -7238,37 +7219,37 @@
         <v>15</v>
       </c>
       <c r="B101" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>505</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>506</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="K101" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>507</v>
       </c>
       <c r="L101" s="3"/>
       <c r="M101" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N101" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="O101" s="3"/>
     </row>
@@ -7277,37 +7258,37 @@
         <v>114</v>
       </c>
       <c r="B102" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>510</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>511</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="K102" s="3" t="s">
         <v>511</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>512</v>
       </c>
       <c r="L102" s="3"/>
       <c r="M102" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N102" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="O102" s="3"/>
     </row>
@@ -7316,37 +7297,37 @@
         <v>15</v>
       </c>
       <c r="B103" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>515</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>516</v>
       </c>
       <c r="D103" s="3"/>
       <c r="E103" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="J103" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="K103" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="J103" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="K103" s="3" t="s">
-        <v>517</v>
       </c>
       <c r="L103" s="3"/>
       <c r="M103" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N103" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="O103" s="3"/>
     </row>
@@ -7355,37 +7336,37 @@
         <v>15</v>
       </c>
       <c r="B104" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>520</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>521</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H104" s="3"/>
       <c r="I104" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="K104" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="J104" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="K104" s="3" t="s">
-        <v>522</v>
       </c>
       <c r="L104" s="3"/>
       <c r="M104" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N104" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="O104" s="3"/>
     </row>
@@ -7394,37 +7375,37 @@
         <v>15</v>
       </c>
       <c r="B105" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C105" s="3" t="s">
         <v>525</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>526</v>
       </c>
       <c r="D105" s="3"/>
       <c r="E105" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="J105" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="K105" s="3" t="s">
         <v>526</v>
-      </c>
-      <c r="J105" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="K105" s="3" t="s">
-        <v>527</v>
       </c>
       <c r="L105" s="3"/>
       <c r="M105" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="O105" s="3"/>
     </row>
@@ -7433,37 +7414,37 @@
         <v>15</v>
       </c>
       <c r="B106" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>530</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="D106" s="3"/>
       <c r="E106" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G106" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="K106" s="3" t="s">
         <v>531</v>
-      </c>
-      <c r="J106" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="K106" s="3" t="s">
-        <v>532</v>
       </c>
       <c r="L106" s="3"/>
       <c r="M106" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N106" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="O106" s="3"/>
     </row>
@@ -7472,37 +7453,37 @@
         <v>15</v>
       </c>
       <c r="B107" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C107" s="3" t="s">
         <v>535</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>536</v>
       </c>
       <c r="D107" s="3"/>
       <c r="E107" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H107" s="3"/>
       <c r="I107" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="J107" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="K107" s="3" t="s">
         <v>536</v>
-      </c>
-      <c r="J107" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="K107" s="3" t="s">
-        <v>537</v>
       </c>
       <c r="L107" s="3"/>
       <c r="M107" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N107" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="O107" s="3"/>
     </row>
@@ -7511,37 +7492,37 @@
         <v>15</v>
       </c>
       <c r="B108" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>540</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>541</v>
       </c>
       <c r="D108" s="3"/>
       <c r="E108" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H108" s="3"/>
       <c r="I108" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="J108" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="K108" s="3" t="s">
         <v>541</v>
-      </c>
-      <c r="J108" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="K108" s="3" t="s">
-        <v>542</v>
       </c>
       <c r="L108" s="3"/>
       <c r="M108" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N108" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="O108" s="3"/>
     </row>
@@ -7550,37 +7531,37 @@
         <v>15</v>
       </c>
       <c r="B109" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>546</v>
       </c>
       <c r="D109" s="3"/>
       <c r="E109" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H109" s="3"/>
       <c r="I109" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="J109" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="K109" s="3" t="s">
         <v>546</v>
-      </c>
-      <c r="J109" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="K109" s="3" t="s">
-        <v>547</v>
       </c>
       <c r="L109" s="3"/>
       <c r="M109" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="O109" s="3"/>
     </row>
@@ -7589,37 +7570,37 @@
         <v>15</v>
       </c>
       <c r="B110" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>551</v>
       </c>
       <c r="D110" s="3"/>
       <c r="E110" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H110" s="3"/>
       <c r="I110" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="K110" s="3" t="s">
         <v>551</v>
-      </c>
-      <c r="J110" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="K110" s="3" t="s">
-        <v>552</v>
       </c>
       <c r="L110" s="3"/>
       <c r="M110" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N110" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="O110" s="3"/>
     </row>
@@ -7628,37 +7609,37 @@
         <v>15</v>
       </c>
       <c r="B111" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>555</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>556</v>
       </c>
       <c r="D111" s="3"/>
       <c r="E111" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H111" s="3"/>
       <c r="I111" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="J111" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="K111" s="3" t="s">
         <v>556</v>
-      </c>
-      <c r="J111" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="K111" s="3" t="s">
-        <v>557</v>
       </c>
       <c r="L111" s="3"/>
       <c r="M111" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="O111" s="3"/>
     </row>
@@ -7667,37 +7648,37 @@
         <v>114</v>
       </c>
       <c r="B112" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>560</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>561</v>
       </c>
       <c r="D112" s="3"/>
       <c r="E112" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G112" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H112" s="3"/>
       <c r="I112" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="K112" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="J112" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="K112" s="3" t="s">
-        <v>562</v>
       </c>
       <c r="L112" s="3"/>
       <c r="M112" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N112" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="O112" s="3"/>
     </row>
@@ -7706,37 +7687,37 @@
         <v>15</v>
       </c>
       <c r="B113" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>565</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>566</v>
       </c>
       <c r="D113" s="3"/>
       <c r="E113" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H113" s="3"/>
       <c r="I113" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="J113" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="K113" s="3" t="s">
         <v>566</v>
-      </c>
-      <c r="J113" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="K113" s="3" t="s">
-        <v>567</v>
       </c>
       <c r="L113" s="3"/>
       <c r="M113" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="O113" s="3"/>
     </row>
@@ -7745,37 +7726,37 @@
         <v>15</v>
       </c>
       <c r="B114" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="C114" s="3" t="s">
         <v>570</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>571</v>
       </c>
       <c r="D114" s="3"/>
       <c r="E114" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H114" s="3"/>
       <c r="I114" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="K114" s="3" t="s">
         <v>571</v>
-      </c>
-      <c r="J114" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="K114" s="3" t="s">
-        <v>572</v>
       </c>
       <c r="L114" s="3"/>
       <c r="M114" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N114" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="O114" s="3"/>
     </row>
@@ -7784,37 +7765,37 @@
         <v>15</v>
       </c>
       <c r="B115" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="C115" s="3" t="s">
         <v>575</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>576</v>
       </c>
       <c r="D115" s="3"/>
       <c r="E115" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H115" s="3"/>
       <c r="I115" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="J115" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="K115" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="J115" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="K115" s="3" t="s">
-        <v>577</v>
       </c>
       <c r="L115" s="3"/>
       <c r="M115" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N115" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="O115" s="3"/>
     </row>
@@ -7823,37 +7804,37 @@
         <v>15</v>
       </c>
       <c r="B116" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C116" s="3" t="s">
         <v>580</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>581</v>
       </c>
       <c r="D116" s="3"/>
       <c r="E116" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G116" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H116" s="3"/>
       <c r="I116" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="K116" s="3" t="s">
         <v>581</v>
-      </c>
-      <c r="J116" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="K116" s="3" t="s">
-        <v>582</v>
       </c>
       <c r="L116" s="3"/>
       <c r="M116" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N116" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O116" s="3"/>
     </row>
@@ -7862,37 +7843,37 @@
         <v>15</v>
       </c>
       <c r="B117" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="C117" s="3" t="s">
         <v>585</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>586</v>
       </c>
       <c r="D117" s="3"/>
       <c r="E117" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H117" s="3"/>
       <c r="I117" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="J117" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="K117" s="3" t="s">
         <v>586</v>
-      </c>
-      <c r="J117" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="K117" s="3" t="s">
-        <v>587</v>
       </c>
       <c r="L117" s="3"/>
       <c r="M117" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="O117" s="3"/>
     </row>
@@ -7901,37 +7882,37 @@
         <v>15</v>
       </c>
       <c r="B118" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C118" s="3" t="s">
         <v>590</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>591</v>
       </c>
       <c r="D118" s="3"/>
       <c r="E118" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H118" s="3"/>
       <c r="I118" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="K118" s="3" t="s">
         <v>591</v>
-      </c>
-      <c r="J118" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="K118" s="3" t="s">
-        <v>592</v>
       </c>
       <c r="L118" s="3"/>
       <c r="M118" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N118" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="O118" s="3"/>
     </row>
@@ -7940,37 +7921,37 @@
         <v>15</v>
       </c>
       <c r="B119" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="C119" s="3" t="s">
         <v>595</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>596</v>
       </c>
       <c r="D119" s="3"/>
       <c r="E119" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H119" s="3"/>
       <c r="I119" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="J119" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="K119" s="3" t="s">
         <v>596</v>
-      </c>
-      <c r="J119" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="K119" s="3" t="s">
-        <v>597</v>
       </c>
       <c r="L119" s="3"/>
       <c r="M119" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N119" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="O119" s="3"/>
     </row>
@@ -7979,37 +7960,37 @@
         <v>15</v>
       </c>
       <c r="B120" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C120" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>601</v>
       </c>
       <c r="D120" s="3"/>
       <c r="E120" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H120" s="3"/>
       <c r="I120" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="K120" s="3" t="s">
         <v>601</v>
-      </c>
-      <c r="J120" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="K120" s="3" t="s">
-        <v>602</v>
       </c>
       <c r="L120" s="3"/>
       <c r="M120" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N120" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="O120" s="3"/>
     </row>
@@ -8018,37 +7999,37 @@
         <v>15</v>
       </c>
       <c r="B121" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="C121" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>606</v>
       </c>
       <c r="D121" s="3"/>
       <c r="E121" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H121" s="3"/>
       <c r="I121" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="J121" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="K121" s="3" t="s">
         <v>606</v>
-      </c>
-      <c r="J121" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="K121" s="3" t="s">
-        <v>607</v>
       </c>
       <c r="L121" s="3"/>
       <c r="M121" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N121" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O121" s="3"/>
     </row>
@@ -8057,37 +8038,37 @@
         <v>114</v>
       </c>
       <c r="B122" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="C122" s="3" t="s">
         <v>610</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>611</v>
       </c>
       <c r="D122" s="3"/>
       <c r="E122" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H122" s="3"/>
       <c r="I122" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="K122" s="3" t="s">
         <v>611</v>
-      </c>
-      <c r="J122" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="K122" s="3" t="s">
-        <v>612</v>
       </c>
       <c r="L122" s="3"/>
       <c r="M122" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N122" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="O122" s="3"/>
     </row>
@@ -8096,37 +8077,37 @@
         <v>114</v>
       </c>
       <c r="B123" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C123" s="3" t="s">
         <v>615</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>616</v>
       </c>
       <c r="D123" s="3"/>
       <c r="E123" s="3" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H123" s="3"/>
       <c r="I123" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="J123" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="K123" s="3" t="s">
         <v>616</v>
-      </c>
-      <c r="J123" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="K123" s="3" t="s">
-        <v>617</v>
       </c>
       <c r="L123" s="3"/>
       <c r="M123" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N123" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="O123" s="3"/>
     </row>
@@ -8135,37 +8116,37 @@
         <v>15</v>
       </c>
       <c r="B124" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="C124" s="3" t="s">
         <v>620</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>621</v>
       </c>
       <c r="D124" s="3"/>
       <c r="E124" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H124" s="3"/>
       <c r="I124" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="K124" s="3" t="s">
         <v>621</v>
-      </c>
-      <c r="J124" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="K124" s="3" t="s">
-        <v>622</v>
       </c>
       <c r="L124" s="3"/>
       <c r="M124" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N124" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="O124" s="3"/>
     </row>
@@ -8174,37 +8155,37 @@
         <v>15</v>
       </c>
       <c r="B125" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C125" s="3" t="s">
         <v>625</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>626</v>
       </c>
       <c r="D125" s="3"/>
       <c r="E125" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H125" s="3"/>
       <c r="I125" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="K125" s="3" t="s">
         <v>626</v>
-      </c>
-      <c r="J125" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="K125" s="3" t="s">
-        <v>627</v>
       </c>
       <c r="L125" s="3"/>
       <c r="M125" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N125" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="O125" s="3"/>
     </row>
@@ -8213,37 +8194,37 @@
         <v>114</v>
       </c>
       <c r="B126" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="C126" s="3" t="s">
         <v>630</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>631</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G126" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H126" s="3"/>
       <c r="I126" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="K126" s="3" t="s">
         <v>631</v>
-      </c>
-      <c r="J126" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="K126" s="3" t="s">
-        <v>632</v>
       </c>
       <c r="L126" s="3"/>
       <c r="M126" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N126" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="O126" s="3"/>
     </row>
@@ -8252,37 +8233,37 @@
         <v>15</v>
       </c>
       <c r="B127" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="C127" s="3" t="s">
         <v>635</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>636</v>
       </c>
       <c r="D127" s="3"/>
       <c r="E127" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H127" s="3"/>
       <c r="I127" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="K127" s="3" t="s">
         <v>636</v>
-      </c>
-      <c r="J127" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="K127" s="3" t="s">
-        <v>637</v>
       </c>
       <c r="L127" s="3"/>
       <c r="M127" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N127" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="O127" s="3"/>
     </row>
@@ -8291,37 +8272,37 @@
         <v>15</v>
       </c>
       <c r="B128" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C128" s="3" t="s">
         <v>640</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>641</v>
       </c>
       <c r="D128" s="3"/>
       <c r="E128" s="3" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H128" s="3"/>
       <c r="I128" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="J128" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="K128" s="3" t="s">
         <v>641</v>
-      </c>
-      <c r="J128" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="K128" s="3" t="s">
-        <v>642</v>
       </c>
       <c r="L128" s="3"/>
       <c r="M128" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N128" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="O128" s="3"/>
     </row>
@@ -8330,37 +8311,37 @@
         <v>15</v>
       </c>
       <c r="B129" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>645</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>646</v>
       </c>
       <c r="D129" s="3"/>
       <c r="E129" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H129" s="3"/>
       <c r="I129" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="J129" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="J129" s="3" t="s">
-        <v>647</v>
-      </c>
       <c r="K129" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="L129" s="3"/>
       <c r="M129" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N129" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="O129" s="3"/>
     </row>
@@ -8369,35 +8350,35 @@
         <v>114</v>
       </c>
       <c r="B130" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C130" s="3" t="s">
         <v>649</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>650</v>
       </c>
       <c r="D130" s="3"/>
       <c r="E130" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H130" s="3"/>
       <c r="I130" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="J130" s="3"/>
       <c r="K130" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="L130" s="3"/>
       <c r="M130" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N130" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="O130" s="3"/>
     </row>
@@ -8406,37 +8387,37 @@
         <v>15</v>
       </c>
       <c r="B131" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C131" s="3" t="s">
         <v>653</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>654</v>
       </c>
       <c r="D131" s="3"/>
       <c r="E131" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H131" s="3"/>
       <c r="I131" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="J131" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="K131" s="3" t="s">
         <v>654</v>
-      </c>
-      <c r="J131" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="K131" s="3" t="s">
-        <v>655</v>
       </c>
       <c r="L131" s="3"/>
       <c r="M131" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N131" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="O131" s="3"/>
     </row>
@@ -8445,37 +8426,37 @@
         <v>15</v>
       </c>
       <c r="B132" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="C132" s="3" t="s">
         <v>658</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>659</v>
       </c>
       <c r="D132" s="3"/>
       <c r="E132" s="3" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G132" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H132" s="3"/>
       <c r="I132" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="J132" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="K132" s="3" t="s">
         <v>659</v>
-      </c>
-      <c r="J132" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="K132" s="3" t="s">
-        <v>660</v>
       </c>
       <c r="L132" s="3"/>
       <c r="M132" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N132" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="O132" s="3"/>
     </row>
@@ -8484,37 +8465,37 @@
         <v>15</v>
       </c>
       <c r="B133" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C133" s="3" t="s">
         <v>663</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>664</v>
       </c>
       <c r="D133" s="3"/>
       <c r="E133" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H133" s="3"/>
       <c r="I133" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="J133" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="K133" s="3" t="s">
         <v>664</v>
-      </c>
-      <c r="J133" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="K133" s="3" t="s">
-        <v>665</v>
       </c>
       <c r="L133" s="3"/>
       <c r="M133" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N133" s="3" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="O133" s="3"/>
     </row>
@@ -8523,37 +8504,37 @@
         <v>114</v>
       </c>
       <c r="B134" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C134" s="3" t="s">
         <v>668</v>
-      </c>
-      <c r="C134" s="3" t="s">
-        <v>669</v>
       </c>
       <c r="D134" s="3"/>
       <c r="E134" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H134" s="3"/>
       <c r="I134" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="J134" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="K134" s="3" t="s">
         <v>669</v>
-      </c>
-      <c r="J134" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="K134" s="3" t="s">
-        <v>670</v>
       </c>
       <c r="L134" s="3"/>
       <c r="M134" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N134" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="O134" s="3"/>
     </row>
@@ -8562,37 +8543,37 @@
         <v>15</v>
       </c>
       <c r="B135" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="C135" s="3" t="s">
         <v>673</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>674</v>
       </c>
       <c r="D135" s="3"/>
       <c r="E135" s="3" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H135" s="3"/>
       <c r="I135" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="J135" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="K135" s="3" t="s">
         <v>674</v>
-      </c>
-      <c r="J135" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="K135" s="3" t="s">
-        <v>675</v>
       </c>
       <c r="L135" s="3"/>
       <c r="M135" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N135" s="3" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="O135" s="3"/>
     </row>
@@ -8601,37 +8582,37 @@
         <v>15</v>
       </c>
       <c r="B136" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="C136" s="3" t="s">
         <v>678</v>
-      </c>
-      <c r="C136" s="3" t="s">
-        <v>679</v>
       </c>
       <c r="D136" s="3"/>
       <c r="E136" s="3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H136" s="3"/>
       <c r="I136" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="J136" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="K136" s="3" t="s">
         <v>679</v>
-      </c>
-      <c r="J136" s="3" t="s">
-        <v>681</v>
-      </c>
-      <c r="K136" s="3" t="s">
-        <v>680</v>
       </c>
       <c r="L136" s="3"/>
       <c r="M136" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N136" s="3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="O136" s="3"/>
     </row>
@@ -8640,37 +8621,37 @@
         <v>114</v>
       </c>
       <c r="B137" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="C137" s="3" t="s">
         <v>683</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>684</v>
       </c>
       <c r="D137" s="3"/>
       <c r="E137" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H137" s="3"/>
       <c r="I137" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="J137" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="K137" s="3" t="s">
         <v>684</v>
-      </c>
-      <c r="J137" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="K137" s="3" t="s">
-        <v>685</v>
       </c>
       <c r="L137" s="3"/>
       <c r="M137" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N137" s="3" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="O137" s="3"/>
     </row>
@@ -8679,37 +8660,37 @@
         <v>114</v>
       </c>
       <c r="B138" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="C138" s="3" t="s">
         <v>688</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>689</v>
       </c>
       <c r="D138" s="3"/>
       <c r="E138" s="3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H138" s="3"/>
       <c r="I138" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="J138" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="K138" s="3" t="s">
         <v>689</v>
-      </c>
-      <c r="J138" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="K138" s="3" t="s">
-        <v>690</v>
       </c>
       <c r="L138" s="3"/>
       <c r="M138" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N138" s="3" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="O138" s="3"/>
     </row>
@@ -8718,37 +8699,37 @@
         <v>15</v>
       </c>
       <c r="B139" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="C139" s="3" t="s">
         <v>693</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>694</v>
       </c>
       <c r="D139" s="3"/>
       <c r="E139" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H139" s="3"/>
       <c r="I139" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="K139" s="3" t="s">
         <v>694</v>
-      </c>
-      <c r="J139" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="K139" s="3" t="s">
-        <v>695</v>
       </c>
       <c r="L139" s="3"/>
       <c r="M139" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N139" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="O139" s="3"/>
     </row>
@@ -8757,37 +8738,37 @@
         <v>114</v>
       </c>
       <c r="B140" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>698</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>699</v>
       </c>
       <c r="D140" s="3"/>
       <c r="E140" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H140" s="3"/>
       <c r="I140" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="J140" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="K140" s="3" t="s">
         <v>699</v>
-      </c>
-      <c r="J140" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="K140" s="3" t="s">
-        <v>700</v>
       </c>
       <c r="L140" s="3"/>
       <c r="M140" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N140" s="3" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="O140" s="3"/>
     </row>
@@ -8796,260 +8777,252 @@
         <v>15</v>
       </c>
       <c r="B141" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="C141" s="3" t="s">
         <v>703</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>704</v>
       </c>
       <c r="D141" s="3"/>
       <c r="E141" s="3" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H141" s="3"/>
       <c r="I141" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="J141" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="K141" s="3" t="s">
         <v>704</v>
-      </c>
-      <c r="J141" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="K141" s="3" t="s">
-        <v>705</v>
       </c>
       <c r="L141" s="3"/>
       <c r="M141" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N141" s="3" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="O141" s="3"/>
     </row>
     <row r="142" spans="1:15" ht="24" customHeight="1">
       <c r="A142" s="3" t="s">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="B142" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="C142" s="3" t="s">
         <v>708</v>
-      </c>
-      <c r="C142" s="3" t="s">
-        <v>709</v>
       </c>
       <c r="D142" s="3"/>
       <c r="E142" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H142" s="3"/>
       <c r="I142" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="J142" s="3"/>
+      <c r="K142" s="3" t="s">
         <v>709</v>
-      </c>
-      <c r="J142" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="K142" s="3" t="s">
-        <v>710</v>
       </c>
       <c r="L142" s="3"/>
       <c r="M142" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="N142" s="3" t="s">
-        <v>712</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="N142" s="3"/>
       <c r="O142" s="3"/>
     </row>
     <row r="143" spans="1:15" ht="24" customHeight="1">
       <c r="A143" s="3" t="s">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D143" s="3"/>
       <c r="E143" s="3" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H143" s="3"/>
       <c r="I143" s="3" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="J143" s="3"/>
       <c r="K143" s="3" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="L143" s="3"/>
       <c r="M143" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="N143" s="3"/>
       <c r="O143" s="3"/>
     </row>
     <row r="144" spans="1:15" ht="24" customHeight="1">
       <c r="A144" s="3" t="s">
-        <v>114</v>
+        <v>15</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D144" s="3"/>
       <c r="E144" s="3" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G144" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H144" s="3"/>
       <c r="I144" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="J144" s="3"/>
+        <v>714</v>
+      </c>
+      <c r="J144" s="3" t="s">
+        <v>716</v>
+      </c>
       <c r="K144" s="3" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="L144" s="3"/>
       <c r="M144" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="N144" s="3"/>
+        <v>442</v>
+      </c>
+      <c r="N144" s="3" t="s">
+        <v>717</v>
+      </c>
       <c r="O144" s="3"/>
     </row>
     <row r="145" spans="1:15" ht="24" customHeight="1">
       <c r="A145" s="3" t="s">
-        <v>114</v>
+        <v>15</v>
       </c>
       <c r="B145" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="C145" s="3" t="s">
         <v>719</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>720</v>
       </c>
       <c r="D145" s="3"/>
       <c r="E145" s="3" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G145" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H145" s="3"/>
       <c r="I145" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="J145" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="K145" s="3" t="s">
         <v>720</v>
-      </c>
-      <c r="J145" s="3"/>
-      <c r="K145" s="3" t="s">
-        <v>721</v>
       </c>
       <c r="L145" s="3"/>
       <c r="M145" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="N145" s="3"/>
+        <v>442</v>
+      </c>
+      <c r="N145" s="3" t="s">
+        <v>722</v>
+      </c>
       <c r="O145" s="3"/>
     </row>
     <row r="146" spans="1:15" ht="24" customHeight="1">
       <c r="A146" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B146" s="3" t="s">
-        <v>722</v>
+      <c r="B146" s="3">
+        <v>800</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="D146" s="3"/>
+      <c r="D146" s="3" t="s">
+        <v>117</v>
+      </c>
       <c r="E146" s="3" t="s">
         <v>724</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>441</v>
+        <v>20</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>20</v>
+        <v>440</v>
       </c>
       <c r="H146" s="3"/>
-      <c r="I146" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="J146" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="K146" s="3" t="s">
-        <v>724</v>
-      </c>
+      <c r="I146" s="3"/>
+      <c r="J146" s="3"/>
+      <c r="K146" s="3"/>
       <c r="L146" s="3"/>
       <c r="M146" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="N146" s="3" t="s">
-        <v>726</v>
-      </c>
+        <v>725</v>
+      </c>
+      <c r="N146" s="3"/>
       <c r="O146" s="3"/>
     </row>
     <row r="147" spans="1:15" ht="24" customHeight="1">
       <c r="A147" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="3">
+        <v>801</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E147" s="3" t="s">
         <v>727</v>
       </c>
-      <c r="C147" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="D147" s="3"/>
-      <c r="E147" s="3" t="s">
-        <v>729</v>
-      </c>
       <c r="F147" s="3" t="s">
-        <v>441</v>
+        <v>20</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>20</v>
+        <v>440</v>
       </c>
       <c r="H147" s="3"/>
-      <c r="I147" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J147" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="K147" s="3" t="s">
-        <v>729</v>
-      </c>
+      <c r="I147" s="3"/>
+      <c r="J147" s="3"/>
+      <c r="K147" s="3"/>
       <c r="L147" s="3"/>
       <c r="M147" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="N147" s="3" t="s">
-        <v>731</v>
-      </c>
+        <v>725</v>
+      </c>
+      <c r="N147" s="3"/>
       <c r="O147" s="3"/>
     </row>
     <row r="148" spans="1:15" ht="24" customHeight="1">
@@ -9057,22 +9030,22 @@
         <v>15</v>
       </c>
       <c r="B148" s="3">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H148" s="3"/>
       <c r="I148" s="3"/>
@@ -9080,7 +9053,7 @@
       <c r="K148" s="3"/>
       <c r="L148" s="3"/>
       <c r="M148" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N148" s="3"/>
       <c r="O148" s="3"/>
@@ -9090,22 +9063,20 @@
         <v>15</v>
       </c>
       <c r="B149" s="3">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E149" s="3" t="s">
-        <v>736</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E149" s="3"/>
       <c r="F149" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H149" s="3"/>
       <c r="I149" s="3"/>
@@ -9113,7 +9084,7 @@
       <c r="K149" s="3"/>
       <c r="L149" s="3"/>
       <c r="M149" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N149" s="3"/>
       <c r="O149" s="3"/>
@@ -9123,22 +9094,22 @@
         <v>15</v>
       </c>
       <c r="B150" s="3">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H150" s="3"/>
       <c r="I150" s="3"/>
@@ -9146,7 +9117,7 @@
       <c r="K150" s="3"/>
       <c r="L150" s="3"/>
       <c r="M150" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N150" s="3"/>
       <c r="O150" s="3"/>
@@ -9156,20 +9127,22 @@
         <v>15</v>
       </c>
       <c r="B151" s="3">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E151" s="3"/>
+      <c r="E151" s="3" t="s">
+        <v>734</v>
+      </c>
       <c r="F151" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H151" s="3"/>
       <c r="I151" s="3"/>
@@ -9177,7 +9150,7 @@
       <c r="K151" s="3"/>
       <c r="L151" s="3"/>
       <c r="M151" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N151" s="3"/>
       <c r="O151" s="3"/>
@@ -9187,22 +9160,22 @@
         <v>15</v>
       </c>
       <c r="B152" s="3">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H152" s="3"/>
       <c r="I152" s="3"/>
@@ -9210,7 +9183,7 @@
       <c r="K152" s="3"/>
       <c r="L152" s="3"/>
       <c r="M152" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N152" s="3"/>
       <c r="O152" s="3"/>
@@ -9220,22 +9193,22 @@
         <v>15</v>
       </c>
       <c r="B153" s="3">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H153" s="3"/>
       <c r="I153" s="3"/>
@@ -9243,7 +9216,7 @@
       <c r="K153" s="3"/>
       <c r="L153" s="3"/>
       <c r="M153" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N153" s="3"/>
       <c r="O153" s="3"/>
@@ -9253,22 +9226,22 @@
         <v>15</v>
       </c>
       <c r="B154" s="3">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H154" s="3"/>
       <c r="I154" s="3"/>
@@ -9276,7 +9249,7 @@
       <c r="K154" s="3"/>
       <c r="L154" s="3"/>
       <c r="M154" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N154" s="3"/>
       <c r="O154" s="3"/>
@@ -9286,22 +9259,22 @@
         <v>15</v>
       </c>
       <c r="B155" s="3">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H155" s="3"/>
       <c r="I155" s="3"/>
@@ -9309,7 +9282,7 @@
       <c r="K155" s="3"/>
       <c r="L155" s="3"/>
       <c r="M155" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N155" s="3"/>
       <c r="O155" s="3"/>
@@ -9319,22 +9292,22 @@
         <v>15</v>
       </c>
       <c r="B156" s="3">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H156" s="3"/>
       <c r="I156" s="3"/>
@@ -9342,7 +9315,7 @@
       <c r="K156" s="3"/>
       <c r="L156" s="3"/>
       <c r="M156" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N156" s="3"/>
       <c r="O156" s="3"/>
@@ -9352,22 +9325,22 @@
         <v>15</v>
       </c>
       <c r="B157" s="3">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H157" s="3"/>
       <c r="I157" s="3"/>
@@ -9375,7 +9348,7 @@
       <c r="K157" s="3"/>
       <c r="L157" s="3"/>
       <c r="M157" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N157" s="3"/>
       <c r="O157" s="3"/>
@@ -9385,22 +9358,22 @@
         <v>15</v>
       </c>
       <c r="B158" s="3">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H158" s="3"/>
       <c r="I158" s="3"/>
@@ -9408,7 +9381,7 @@
       <c r="K158" s="3"/>
       <c r="L158" s="3"/>
       <c r="M158" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N158" s="3"/>
       <c r="O158" s="3"/>
@@ -9418,22 +9391,22 @@
         <v>15</v>
       </c>
       <c r="B159" s="3">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H159" s="3"/>
       <c r="I159" s="3"/>
@@ -9441,7 +9414,7 @@
       <c r="K159" s="3"/>
       <c r="L159" s="3"/>
       <c r="M159" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N159" s="3"/>
       <c r="O159" s="3"/>
@@ -9451,22 +9424,22 @@
         <v>15</v>
       </c>
       <c r="B160" s="3">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H160" s="3"/>
       <c r="I160" s="3"/>
@@ -9474,7 +9447,7 @@
       <c r="K160" s="3"/>
       <c r="L160" s="3"/>
       <c r="M160" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N160" s="3"/>
       <c r="O160" s="3"/>
@@ -9484,22 +9457,22 @@
         <v>15</v>
       </c>
       <c r="B161" s="3">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H161" s="3"/>
       <c r="I161" s="3"/>
@@ -9507,7 +9480,7 @@
       <c r="K161" s="3"/>
       <c r="L161" s="3"/>
       <c r="M161" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N161" s="3"/>
       <c r="O161" s="3"/>
@@ -9517,22 +9490,22 @@
         <v>15</v>
       </c>
       <c r="B162" s="3">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H162" s="3"/>
       <c r="I162" s="3"/>
@@ -9540,7 +9513,7 @@
       <c r="K162" s="3"/>
       <c r="L162" s="3"/>
       <c r="M162" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N162" s="3"/>
       <c r="O162" s="3"/>
@@ -9550,22 +9523,22 @@
         <v>15</v>
       </c>
       <c r="B163" s="3">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H163" s="3"/>
       <c r="I163" s="3"/>
@@ -9573,7 +9546,7 @@
       <c r="K163" s="3"/>
       <c r="L163" s="3"/>
       <c r="M163" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N163" s="3"/>
       <c r="O163" s="3"/>
@@ -9583,22 +9556,22 @@
         <v>15</v>
       </c>
       <c r="B164" s="3">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H164" s="3"/>
       <c r="I164" s="3"/>
@@ -9606,7 +9579,7 @@
       <c r="K164" s="3"/>
       <c r="L164" s="3"/>
       <c r="M164" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N164" s="3"/>
       <c r="O164" s="3"/>
@@ -9616,22 +9589,22 @@
         <v>15</v>
       </c>
       <c r="B165" s="3">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H165" s="3"/>
       <c r="I165" s="3"/>
@@ -9639,7 +9612,7 @@
       <c r="K165" s="3"/>
       <c r="L165" s="3"/>
       <c r="M165" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N165" s="3"/>
       <c r="O165" s="3"/>
@@ -9649,22 +9622,22 @@
         <v>15</v>
       </c>
       <c r="B166" s="3">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H166" s="3"/>
       <c r="I166" s="3"/>
@@ -9672,7 +9645,7 @@
       <c r="K166" s="3"/>
       <c r="L166" s="3"/>
       <c r="M166" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N166" s="3"/>
       <c r="O166" s="3"/>
@@ -9682,22 +9655,22 @@
         <v>15</v>
       </c>
       <c r="B167" s="3">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H167" s="3"/>
       <c r="I167" s="3"/>
@@ -9705,7 +9678,7 @@
       <c r="K167" s="3"/>
       <c r="L167" s="3"/>
       <c r="M167" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N167" s="3"/>
       <c r="O167" s="3"/>
@@ -9715,22 +9688,22 @@
         <v>15</v>
       </c>
       <c r="B168" s="3">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H168" s="3"/>
       <c r="I168" s="3"/>
@@ -9738,7 +9711,7 @@
       <c r="K168" s="3"/>
       <c r="L168" s="3"/>
       <c r="M168" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N168" s="3"/>
       <c r="O168" s="3"/>
@@ -9748,22 +9721,22 @@
         <v>15</v>
       </c>
       <c r="B169" s="3">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H169" s="3"/>
       <c r="I169" s="3"/>
@@ -9771,7 +9744,7 @@
       <c r="K169" s="3"/>
       <c r="L169" s="3"/>
       <c r="M169" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N169" s="3"/>
       <c r="O169" s="3"/>
@@ -9781,22 +9754,22 @@
         <v>15</v>
       </c>
       <c r="B170" s="3">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H170" s="3"/>
       <c r="I170" s="3"/>
@@ -9804,7 +9777,7 @@
       <c r="K170" s="3"/>
       <c r="L170" s="3"/>
       <c r="M170" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N170" s="3"/>
       <c r="O170" s="3"/>
@@ -9814,22 +9787,22 @@
         <v>15</v>
       </c>
       <c r="B171" s="3">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H171" s="3"/>
       <c r="I171" s="3"/>
@@ -9837,7 +9810,7 @@
       <c r="K171" s="3"/>
       <c r="L171" s="3"/>
       <c r="M171" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N171" s="3"/>
       <c r="O171" s="3"/>
@@ -9847,22 +9820,22 @@
         <v>15</v>
       </c>
       <c r="B172" s="3">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H172" s="3"/>
       <c r="I172" s="3"/>
@@ -9870,7 +9843,7 @@
       <c r="K172" s="3"/>
       <c r="L172" s="3"/>
       <c r="M172" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N172" s="3"/>
       <c r="O172" s="3"/>
@@ -9880,22 +9853,22 @@
         <v>15</v>
       </c>
       <c r="B173" s="3">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H173" s="3"/>
       <c r="I173" s="3"/>
@@ -9903,7 +9876,7 @@
       <c r="K173" s="3"/>
       <c r="L173" s="3"/>
       <c r="M173" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N173" s="3"/>
       <c r="O173" s="3"/>
@@ -9913,22 +9886,22 @@
         <v>15</v>
       </c>
       <c r="B174" s="3">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H174" s="3"/>
       <c r="I174" s="3"/>
@@ -9936,7 +9909,7 @@
       <c r="K174" s="3"/>
       <c r="L174" s="3"/>
       <c r="M174" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N174" s="3"/>
       <c r="O174" s="3"/>
@@ -9946,22 +9919,22 @@
         <v>15</v>
       </c>
       <c r="B175" s="3">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E175" s="3" t="s">
-        <v>787</v>
+      <c r="E175" s="4" t="s">
+        <v>853</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H175" s="3"/>
       <c r="I175" s="3"/>
@@ -9969,7 +9942,7 @@
       <c r="K175" s="3"/>
       <c r="L175" s="3"/>
       <c r="M175" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N175" s="3"/>
       <c r="O175" s="3"/>
@@ -9979,22 +9952,22 @@
         <v>15</v>
       </c>
       <c r="B176" s="3">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H176" s="3"/>
       <c r="I176" s="3"/>
@@ -10002,7 +9975,7 @@
       <c r="K176" s="3"/>
       <c r="L176" s="3"/>
       <c r="M176" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N176" s="3"/>
       <c r="O176" s="3"/>
@@ -10012,22 +9985,22 @@
         <v>15</v>
       </c>
       <c r="B177" s="3">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E177" s="4" t="s">
-        <v>862</v>
+      <c r="E177" s="3" t="s">
+        <v>785</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H177" s="3"/>
       <c r="I177" s="3"/>
@@ -10035,7 +10008,7 @@
       <c r="K177" s="3"/>
       <c r="L177" s="3"/>
       <c r="M177" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N177" s="3"/>
       <c r="O177" s="3"/>
@@ -10045,22 +10018,22 @@
         <v>15</v>
       </c>
       <c r="B178" s="3">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H178" s="3"/>
       <c r="I178" s="3"/>
@@ -10068,7 +10041,7 @@
       <c r="K178" s="3"/>
       <c r="L178" s="3"/>
       <c r="M178" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N178" s="3"/>
       <c r="O178" s="3"/>
@@ -10078,22 +10051,22 @@
         <v>15</v>
       </c>
       <c r="B179" s="3">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="D179" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H179" s="3"/>
       <c r="I179" s="3"/>
@@ -10101,7 +10074,7 @@
       <c r="K179" s="3"/>
       <c r="L179" s="3"/>
       <c r="M179" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N179" s="3"/>
       <c r="O179" s="3"/>
@@ -10111,22 +10084,22 @@
         <v>15</v>
       </c>
       <c r="B180" s="3">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>18</v>
+        <v>791</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H180" s="3"/>
       <c r="I180" s="3"/>
@@ -10134,7 +10107,7 @@
       <c r="K180" s="3"/>
       <c r="L180" s="3"/>
       <c r="M180" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N180" s="3"/>
       <c r="O180" s="3"/>
@@ -10144,22 +10117,22 @@
         <v>15</v>
       </c>
       <c r="B181" s="3">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="D181" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E181" s="3" t="s">
-        <v>798</v>
+      <c r="E181" s="4" t="s">
+        <v>854</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H181" s="3"/>
       <c r="I181" s="3"/>
@@ -10167,7 +10140,7 @@
       <c r="K181" s="3"/>
       <c r="L181" s="3"/>
       <c r="M181" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N181" s="3"/>
       <c r="O181" s="3"/>
@@ -10177,22 +10150,22 @@
         <v>15</v>
       </c>
       <c r="B182" s="3">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>800</v>
+        <v>18</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H182" s="3"/>
       <c r="I182" s="3"/>
@@ -10200,7 +10173,7 @@
       <c r="K182" s="3"/>
       <c r="L182" s="3"/>
       <c r="M182" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N182" s="3"/>
       <c r="O182" s="3"/>
@@ -10210,22 +10183,22 @@
         <v>15</v>
       </c>
       <c r="B183" s="3">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E183" s="4" t="s">
-        <v>863</v>
+        <v>117</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>797</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H183" s="3"/>
       <c r="I183" s="3"/>
@@ -10233,7 +10206,7 @@
       <c r="K183" s="3"/>
       <c r="L183" s="3"/>
       <c r="M183" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N183" s="3"/>
       <c r="O183" s="3"/>
@@ -10243,22 +10216,22 @@
         <v>15</v>
       </c>
       <c r="B184" s="3">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H184" s="3"/>
       <c r="I184" s="3"/>
@@ -10266,7 +10239,7 @@
       <c r="K184" s="3"/>
       <c r="L184" s="3"/>
       <c r="M184" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N184" s="3"/>
       <c r="O184" s="3"/>
@@ -10276,22 +10249,22 @@
         <v>15</v>
       </c>
       <c r="B185" s="3">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H185" s="3"/>
       <c r="I185" s="3"/>
@@ -10299,7 +10272,7 @@
       <c r="K185" s="3"/>
       <c r="L185" s="3"/>
       <c r="M185" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N185" s="3"/>
       <c r="O185" s="3"/>
@@ -10309,22 +10282,22 @@
         <v>15</v>
       </c>
       <c r="B186" s="3">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="D186" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H186" s="3"/>
       <c r="I186" s="3"/>
@@ -10332,7 +10305,7 @@
       <c r="K186" s="3"/>
       <c r="L186" s="3"/>
       <c r="M186" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N186" s="3"/>
       <c r="O186" s="3"/>
@@ -10342,22 +10315,22 @@
         <v>15</v>
       </c>
       <c r="B187" s="3">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="D187" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H187" s="3"/>
       <c r="I187" s="3"/>
@@ -10365,7 +10338,7 @@
       <c r="K187" s="3"/>
       <c r="L187" s="3"/>
       <c r="M187" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N187" s="3"/>
       <c r="O187" s="3"/>
@@ -10375,22 +10348,22 @@
         <v>15</v>
       </c>
       <c r="B188" s="3">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H188" s="3"/>
       <c r="I188" s="3"/>
@@ -10398,7 +10371,7 @@
       <c r="K188" s="3"/>
       <c r="L188" s="3"/>
       <c r="M188" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N188" s="3"/>
       <c r="O188" s="3"/>
@@ -10408,22 +10381,22 @@
         <v>15</v>
       </c>
       <c r="B189" s="3">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="D189" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H189" s="3"/>
       <c r="I189" s="3"/>
@@ -10431,7 +10404,7 @@
       <c r="K189" s="3"/>
       <c r="L189" s="3"/>
       <c r="M189" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N189" s="3"/>
       <c r="O189" s="3"/>
@@ -10441,22 +10414,20 @@
         <v>15</v>
       </c>
       <c r="B190" s="3">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E190" s="3" t="s">
-        <v>816</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E190" s="3"/>
       <c r="F190" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H190" s="3"/>
       <c r="I190" s="3"/>
@@ -10464,7 +10435,7 @@
       <c r="K190" s="3"/>
       <c r="L190" s="3"/>
       <c r="M190" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N190" s="3"/>
       <c r="O190" s="3"/>
@@ -10474,22 +10445,22 @@
         <v>15</v>
       </c>
       <c r="B191" s="3">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="D191" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H191" s="3"/>
       <c r="I191" s="3"/>
@@ -10497,7 +10468,7 @@
       <c r="K191" s="3"/>
       <c r="L191" s="3"/>
       <c r="M191" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N191" s="3"/>
       <c r="O191" s="3"/>
@@ -10507,20 +10478,22 @@
         <v>15</v>
       </c>
       <c r="B192" s="3">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E192" s="3"/>
+      <c r="E192" s="3" t="s">
+        <v>814</v>
+      </c>
       <c r="F192" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H192" s="3"/>
       <c r="I192" s="3"/>
@@ -10528,7 +10501,7 @@
       <c r="K192" s="3"/>
       <c r="L192" s="3"/>
       <c r="M192" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N192" s="3"/>
       <c r="O192" s="3"/>
@@ -10538,22 +10511,22 @@
         <v>15</v>
       </c>
       <c r="B193" s="3">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>18</v>
+        <v>791</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H193" s="3"/>
       <c r="I193" s="3"/>
@@ -10561,7 +10534,7 @@
       <c r="K193" s="3"/>
       <c r="L193" s="3"/>
       <c r="M193" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N193" s="3"/>
       <c r="O193" s="3"/>
@@ -10571,22 +10544,22 @@
         <v>15</v>
       </c>
       <c r="B194" s="3">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H194" s="3"/>
       <c r="I194" s="3"/>
@@ -10594,7 +10567,7 @@
       <c r="K194" s="3"/>
       <c r="L194" s="3"/>
       <c r="M194" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N194" s="3"/>
       <c r="O194" s="3"/>
@@ -10604,22 +10577,22 @@
         <v>15</v>
       </c>
       <c r="B195" s="3">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>800</v>
+        <v>18</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H195" s="3"/>
       <c r="I195" s="3"/>
@@ -10627,7 +10600,7 @@
       <c r="K195" s="3"/>
       <c r="L195" s="3"/>
       <c r="M195" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N195" s="3"/>
       <c r="O195" s="3"/>
@@ -10637,22 +10610,22 @@
         <v>15</v>
       </c>
       <c r="B196" s="3">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H196" s="3"/>
       <c r="I196" s="3"/>
@@ -10660,7 +10633,7 @@
       <c r="K196" s="3"/>
       <c r="L196" s="3"/>
       <c r="M196" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N196" s="3"/>
       <c r="O196" s="3"/>
@@ -10670,22 +10643,22 @@
         <v>15</v>
       </c>
       <c r="B197" s="3">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H197" s="3"/>
       <c r="I197" s="3"/>
@@ -10693,7 +10666,7 @@
       <c r="K197" s="3"/>
       <c r="L197" s="3"/>
       <c r="M197" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N197" s="3"/>
       <c r="O197" s="3"/>
@@ -10703,22 +10676,22 @@
         <v>15</v>
       </c>
       <c r="B198" s="3">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H198" s="3"/>
       <c r="I198" s="3"/>
@@ -10726,7 +10699,7 @@
       <c r="K198" s="3"/>
       <c r="L198" s="3"/>
       <c r="M198" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N198" s="3"/>
       <c r="O198" s="3"/>
@@ -10736,22 +10709,22 @@
         <v>15</v>
       </c>
       <c r="B199" s="3">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H199" s="3"/>
       <c r="I199" s="3"/>
@@ -10759,7 +10732,7 @@
       <c r="K199" s="3"/>
       <c r="L199" s="3"/>
       <c r="M199" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N199" s="3"/>
       <c r="O199" s="3"/>
@@ -10769,22 +10742,22 @@
         <v>15</v>
       </c>
       <c r="B200" s="3">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H200" s="3"/>
       <c r="I200" s="3"/>
@@ -10792,7 +10765,7 @@
       <c r="K200" s="3"/>
       <c r="L200" s="3"/>
       <c r="M200" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N200" s="3"/>
       <c r="O200" s="3"/>
@@ -10802,22 +10775,22 @@
         <v>15</v>
       </c>
       <c r="B201" s="3">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>837</v>
+        <v>213</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H201" s="3"/>
       <c r="I201" s="3"/>
@@ -10825,7 +10798,7 @@
       <c r="K201" s="3"/>
       <c r="L201" s="3"/>
       <c r="M201" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N201" s="3"/>
       <c r="O201" s="3"/>
@@ -10835,22 +10808,22 @@
         <v>15</v>
       </c>
       <c r="B202" s="3">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>18</v>
+        <v>791</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H202" s="3"/>
       <c r="I202" s="3"/>
@@ -10858,7 +10831,7 @@
       <c r="K202" s="3"/>
       <c r="L202" s="3"/>
       <c r="M202" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N202" s="3"/>
       <c r="O202" s="3"/>
@@ -10868,22 +10841,22 @@
         <v>15</v>
       </c>
       <c r="B203" s="3">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="D203" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>213</v>
+        <v>835</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H203" s="3"/>
       <c r="I203" s="3"/>
@@ -10891,7 +10864,7 @@
       <c r="K203" s="3"/>
       <c r="L203" s="3"/>
       <c r="M203" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N203" s="3"/>
       <c r="O203" s="3"/>
@@ -10901,22 +10874,22 @@
         <v>15</v>
       </c>
       <c r="B204" s="3">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>800</v>
+        <v>18</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H204" s="3"/>
       <c r="I204" s="3"/>
@@ -10924,7 +10897,7 @@
       <c r="K204" s="3"/>
       <c r="L204" s="3"/>
       <c r="M204" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N204" s="3"/>
       <c r="O204" s="3"/>
@@ -10934,22 +10907,22 @@
         <v>15</v>
       </c>
       <c r="B205" s="3">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H205" s="3"/>
       <c r="I205" s="3"/>
@@ -10957,7 +10930,7 @@
       <c r="K205" s="3"/>
       <c r="L205" s="3"/>
       <c r="M205" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N205" s="3"/>
       <c r="O205" s="3"/>
@@ -10967,22 +10940,22 @@
         <v>15</v>
       </c>
       <c r="B206" s="3">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="D206" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H206" s="3"/>
       <c r="I206" s="3"/>
@@ -10990,7 +10963,7 @@
       <c r="K206" s="3"/>
       <c r="L206" s="3"/>
       <c r="M206" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N206" s="3"/>
       <c r="O206" s="3"/>
@@ -11000,22 +10973,22 @@
         <v>15</v>
       </c>
       <c r="B207" s="3">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H207" s="3"/>
       <c r="I207" s="3"/>
@@ -11023,7 +10996,7 @@
       <c r="K207" s="3"/>
       <c r="L207" s="3"/>
       <c r="M207" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N207" s="3"/>
       <c r="O207" s="3"/>
@@ -11033,22 +11006,22 @@
         <v>15</v>
       </c>
       <c r="B208" s="3">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="D208" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H208" s="3"/>
       <c r="I208" s="3"/>
@@ -11056,7 +11029,7 @@
       <c r="K208" s="3"/>
       <c r="L208" s="3"/>
       <c r="M208" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N208" s="3"/>
       <c r="O208" s="3"/>
@@ -11066,22 +11039,22 @@
         <v>15</v>
       </c>
       <c r="B209" s="3">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H209" s="3"/>
       <c r="I209" s="3"/>
@@ -11089,7 +11062,7 @@
       <c r="K209" s="3"/>
       <c r="L209" s="3"/>
       <c r="M209" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N209" s="3"/>
       <c r="O209" s="3"/>
@@ -11099,22 +11072,22 @@
         <v>15</v>
       </c>
       <c r="B210" s="3">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="D210" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H210" s="3"/>
       <c r="I210" s="3"/>
@@ -11122,7 +11095,7 @@
       <c r="K210" s="3"/>
       <c r="L210" s="3"/>
       <c r="M210" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N210" s="3"/>
       <c r="O210" s="3"/>
@@ -11132,22 +11105,22 @@
         <v>15</v>
       </c>
       <c r="B211" s="3">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>18</v>
+        <v>117</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>856</v>
+        <v>734</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H211" s="3"/>
       <c r="I211" s="3"/>
@@ -11155,79 +11128,17 @@
       <c r="K211" s="3"/>
       <c r="L211" s="3"/>
       <c r="M211" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="N211" s="3"/>
       <c r="O211" s="3"/>
     </row>
-    <row r="212" spans="1:15" ht="24" customHeight="1">
-      <c r="A212" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B212" s="3">
-        <v>864</v>
-      </c>
-      <c r="C212" s="3" t="s">
-        <v>857</v>
-      </c>
-      <c r="D212" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E212" s="3" t="s">
-        <v>858</v>
-      </c>
-      <c r="F212" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G212" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="H212" s="3"/>
-      <c r="I212" s="3"/>
-      <c r="J212" s="3"/>
-      <c r="K212" s="3"/>
-      <c r="L212" s="3"/>
-      <c r="M212" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="N212" s="3"/>
-      <c r="O212" s="3"/>
-    </row>
-    <row r="213" spans="1:15" ht="24" customHeight="1">
-      <c r="A213" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B213" s="3">
-        <v>865</v>
-      </c>
-      <c r="C213" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="D213" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E213" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="F213" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G213" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="H213" s="3"/>
-      <c r="I213" s="3"/>
-      <c r="J213" s="3"/>
-      <c r="K213" s="3"/>
-      <c r="L213" s="3"/>
-      <c r="M213" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="N213" s="3"/>
-      <c r="O213" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O213" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:O211" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A40:O77">
+      <sortCondition ref="B1:B211"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
